--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.729.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.729.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="64">
   <si>
     <t>Property</t>
   </si>
@@ -70,19 +70,7 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ANS (https://esante.gouv.fr)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -351,7 +339,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -443,43 +431,27 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>9</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -498,162 +470,162 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -672,34 +644,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.729.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.729.xlsx
@@ -64,13 +64,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-25T01:00:00+02:00</t>
+    <t>2023-10-25T00:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+    <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -91,6 +91,21 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>GEN-092.08.06</t>
+  </si>
+  <si>
+    <t>Autre trousse</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
+  </si>
+  <si>
     <t>VHEDA1GUR01LX</t>
   </si>
   <si>
@@ -190,22 +205,7 @@
     <t>AB ANALITICA Realquality RQ-HPV Screen - libellé tableau CNRP</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.250.1.213.2.3.5</t>
-  </si>
-  <si>
-    <t>GEN-092.08.06</t>
-  </si>
-  <si>
-    <t>Autre trousse</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
+    <t>1.2.250.1.213.2.3.5</t>
   </si>
 </sst>
 </file>
@@ -461,6 +461,52 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -478,199 +524,153 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>60</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B4" t="s" s="2">
         <v>63</v>
       </c>
     </row>

--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.729.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.729.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="66">
   <si>
     <t>Property</t>
   </si>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -339,7 +345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -431,27 +437,35 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>23</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -470,34 +484,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -516,162 +530,162 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
